--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104535_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104535_W9.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7567</v>
+        <v>5.2833</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3584</v>
+        <v>3.6747</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3983</v>
+        <v>1.6085</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4544</v>
+        <v>4.4514</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6348</v>
+        <v>0.6429</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8196</v>
+        <v>3.8085</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0543</v>
+        <v>3.0268</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1571</v>
+        <v>-1.1656</v>
       </c>
       <c r="L2" t="n">
-        <v>4.2114</v>
+        <v>4.1924</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4001</v>
+        <v>1.4245</v>
       </c>
       <c r="N2" t="n">
-        <v>1.7919</v>
+        <v>1.8085</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1585</v>
+        <v>0.7017</v>
       </c>
       <c r="T2" t="n">
-        <v>0.614</v>
+        <v>0.9729</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4555</v>
+        <v>-0.2713</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0957</v>
+        <v>2.4257</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0231</v>
+        <v>2.3625</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0726</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3643</v>
+        <v>0.206</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4442</v>
+        <v>0.961</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0799</v>
+        <v>-0.755</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6261</v>
+        <v>1.4487</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5888</v>
+        <v>1.2778</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0373</v>
+        <v>0.1708</v>
       </c>
       <c r="M3" t="n">
-        <v>1.7382</v>
+        <v>-1.2426</v>
       </c>
       <c r="N3" t="n">
-        <v>1.8555</v>
+        <v>-0.3168</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1172</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2531</v>
+        <v>0.1789</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4386</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1854</v>
+        <v>-0.5152</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3856</v>
+        <v>2.7237</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>2.7237</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4428</v>
+        <v>2.2004</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5374</v>
+        <v>1.0157</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0946</v>
+        <v>1.1847</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2336</v>
+        <v>2.3765</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9933</v>
+        <v>2.4523</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5066</v>
+        <v>0.6233</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3254</v>
+        <v>0.5861</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1812</v>
+        <v>0.0372</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2729</v>
+        <v>1.7532</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3321</v>
+        <v>1.8663</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9408</v>
+        <v>-0.113</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.842</v>
+        <v>0.3474</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2056</v>
+        <v>0.4411</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6364</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>2.7317</v>
+        <v>0.387</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7317</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8548</v>
+        <v>0.8518</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1428</v>
+        <v>0.8743</v>
       </c>
       <c r="F5" t="n">
-        <v>0.712</v>
+        <v>-0.0225</v>
       </c>
       <c r="G5" t="n">
-        <v>1.316</v>
+        <v>1.0418</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7504</v>
+        <v>3.6561</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4344</v>
+        <v>-2.6142</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5209</v>
+        <v>1.3498</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4462</v>
+        <v>2.6093</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>-1.2595</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7952</v>
+        <v>-0.3079</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3042</v>
+        <v>1.0468</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.509</v>
+        <v>-1.3548</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4952</v>
+        <v>-3.4145</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4462</v>
+        <v>-1.0927</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1171</v>
+        <v>0.0575</v>
       </c>
       <c r="U5" t="n">
-        <v>0.329</v>
+        <v>-1.1502</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>2.7237</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.8814</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5325</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.11</v>
+        <v>0.0553</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6425</v>
+        <v>0.4563</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1901</v>
+        <v>1.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6059</v>
+        <v>1.611</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4158</v>
+        <v>-0.4109</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7167</v>
+        <v>1.698</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0953</v>
+        <v>2.0857</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5266</v>
+        <v>-0.4979</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1836</v>
+        <v>0.1522</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4416</v>
+        <v>0.6337</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.258</v>
+        <v>-0.4815</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.2349</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2499</v>
+        <v>-0.1179</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2581</v>
+        <v>-0.1171</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0273</v>
+        <v>1.0338</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3232</v>
+        <v>1.324</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2958</v>
+        <v>-0.2902</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7863</v>
+        <v>1.7782</v>
       </c>
       <c r="K7" t="n">
-        <v>1.749</v>
+        <v>1.7409</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.759</v>
+        <v>-0.7444</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2643</v>
+        <v>-0.4947</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5958</v>
+        <v>0.2437</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8602</v>
+        <v>-0.7385</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7942</v>
+        <v>-0.614</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1938</v>
+        <v>-1.5537</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6004</v>
+        <v>0.9396</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0401</v>
+        <v>-0.6006</v>
       </c>
       <c r="H8" t="n">
-        <v>3.655</v>
+        <v>1.9585</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6149</v>
+        <v>-2.559</v>
       </c>
       <c r="J8" t="n">
-        <v>1.393</v>
+        <v>-2.0411</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6353</v>
+        <v>0.1789</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2423</v>
+        <v>-2.22</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3529</v>
+        <v>1.4405</v>
       </c>
       <c r="N8" t="n">
-        <v>1.0197</v>
+        <v>1.7796</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3726</v>
+        <v>-0.3391</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.7513</v>
+        <v>-0.311</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0767</v>
+        <v>0.7151</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.6747</v>
+        <v>-1.026</v>
       </c>
       <c r="V8" t="n">
-        <v>2.7317</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8924</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1098</v>
+        <v>-0.8155</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7682</v>
+        <v>-0.9936</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6584</v>
+        <v>0.1781</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6079</v>
+        <v>1.3212</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9537</v>
+        <v>1.7437</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5616</v>
+        <v>-0.4225</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0162</v>
+        <v>0.4979</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1936</v>
+        <v>0.4234</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2098</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4083</v>
+        <v>0.8233</v>
       </c>
       <c r="N9" t="n">
-        <v>1.7601</v>
+        <v>1.3203</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3517</v>
+        <v>-0.497</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7948</v>
+        <v>0.7738</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4748</v>
+        <v>1.0124</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2697</v>
+        <v>-0.2386</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3752</v>
+        <v>-1.6073</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1568</v>
+        <v>-1.9106</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2184</v>
+        <v>0.3033</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4912</v>
+        <v>-1.5909</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2655</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2257</v>
+        <v>-0.6317</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1432</v>
+        <v>-1.562</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6825</v>
+        <v>-0.7724</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4608</v>
+        <v>-0.7896</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.348</v>
+        <v>-0.0289</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5831</v>
+        <v>-0.1868</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7649</v>
+        <v>0.1579</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3695</v>
+        <v>-0.244</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8257</v>
+        <v>-0.3485</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5438</v>
+        <v>0.1046</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6664</v>
+        <v>-2.1307</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9032</v>
+        <v>-1.6875</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2368</v>
+        <v>-0.4433</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5872</v>
+        <v>-3.485</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9581</v>
+        <v>-1.2611</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6291</v>
+        <v>-2.2239</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5554</v>
+        <v>-2.1538</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.769</v>
+        <v>-0.6862</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7864</v>
+        <v>-1.4676</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0318</v>
+        <v>-1.3312</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1891</v>
+        <v>-0.5749</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1573</v>
+        <v>-0.7563</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3061</v>
+        <v>0.6015</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3478</v>
+        <v>0.3085</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0417</v>
+        <v>0.2929</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7589</v>
+        <v>-4.5665</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7959</v>
+        <v>-3.2844</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.963</v>
+        <v>-1.282</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7829</v>
+        <v>-3.7753</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.01</v>
+        <v>-3.0099</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7729</v>
+        <v>-0.7653</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.8749</v>
+        <v>-2.889</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.0242</v>
+        <v>-3.0379</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.908</v>
+        <v>-0.8863</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4097</v>
+        <v>0.5958</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0525</v>
+        <v>0.5849</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3572</v>
+        <v>0.0108</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9698000000000007</v>
+        <v>1.3039</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6163</v>
+        <v>-1.565199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.586100000000001</v>
+        <v>2.8688</v>
       </c>
       <c r="G13" t="n">
-        <v>2.156599999999999</v>
+        <v>2.178900000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>9.126900000000001</v>
+        <v>9.119299999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.9701</v>
+        <v>-6.94</v>
       </c>
       <c r="J13" t="n">
-        <v>2.014200000000002</v>
+        <v>1.776800000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>3.400799999999999</v>
+        <v>3.240000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3868</v>
+        <v>-1.4634</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1425999999999999</v>
+        <v>0.4022999999999998</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7261</v>
+        <v>5.8794</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.5832</v>
+        <v>-5.4772</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.805100000000001</v>
+        <v>-6.829100000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.0126</v>
+        <v>-17.0723</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2074</v>
+        <v>10.2434</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8621000000000001</v>
+        <v>1.2089</v>
       </c>
       <c r="T13" t="n">
-        <v>4.93</v>
+        <v>5.315400000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.0682</v>
+        <v>-4.106700000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>4.7563</v>
+        <v>4.744799999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>8.452300000000001</v>
+        <v>8.4152</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.696</v>
+        <v>-3.6704</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>M. STEINBERGS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5886</v>
+        <v>3.3756</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.9734</v>
+        <v>4.5509</v>
       </c>
       <c r="F14" t="n">
-        <v>4.562</v>
+        <v>-1.1753</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6939</v>
+        <v>3.1703</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3191</v>
+        <v>-1.3161</v>
       </c>
       <c r="I14" t="n">
-        <v>1.013</v>
+        <v>4.4864</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4612</v>
+        <v>3.829</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6478</v>
+        <v>-0.669</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1866</v>
+        <v>4.498</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1551</v>
+        <v>-0.6587</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3288</v>
+        <v>-0.6471</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8264</v>
+        <v>-0.0116</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9647</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7561</v>
+        <v>0.7219</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2085</v>
+        <v>-0.7929</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6105</v>
+        <v>-1.0895</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6105</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. STEINBERGS</t>
+          <t>M. GASPA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5845</v>
+        <v>2.4019</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9745</v>
+        <v>2.3515</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.39</v>
+        <v>0.0505</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1663</v>
+        <v>1.7303</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3277</v>
+        <v>-0.075</v>
       </c>
       <c r="I15" t="n">
-        <v>4.494</v>
+        <v>1.8053</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8475</v>
+        <v>2.589</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6651</v>
+        <v>0.3997</v>
       </c>
       <c r="L15" t="n">
-        <v>4.5126</v>
+        <v>2.1893</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6812</v>
+        <v>-0.8587</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6626</v>
+        <v>-0.4747</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0186</v>
+        <v>-0.384</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8502</v>
+        <v>0.3878</v>
       </c>
       <c r="T15" t="n">
-        <v>0.127</v>
+        <v>-0.1677</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9772</v>
+        <v>0.5554</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0927</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0121</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GASPA</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1714</v>
+        <v>2.2747</v>
       </c>
       <c r="E16" t="n">
-        <v>2.372</v>
+        <v>1.2355</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2006</v>
+        <v>1.0392</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7263</v>
+        <v>2.0803</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0809</v>
+        <v>1.7092</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8072</v>
+        <v>0.3711</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6075</v>
+        <v>1.0178</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4085</v>
+        <v>1.6957</v>
       </c>
       <c r="L16" t="n">
-        <v>2.199</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8812</v>
+        <v>1.0625</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4894</v>
+        <v>0.0135</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3918</v>
+        <v>1.049</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1657</v>
+        <v>0.4749</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1693</v>
+        <v>0.2876</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3351</v>
+        <v>0.1873</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8548</v>
+        <v>-2.1016</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0155</v>
+        <v>-2.2593</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9809</v>
+        <v>1.5637</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7331</v>
+        <v>-2.6912</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2479</v>
+        <v>4.2549</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0836</v>
+        <v>0.7128</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7158</v>
+        <v>-0.3079</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3679</v>
+        <v>1.0207</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0431</v>
+        <v>-0.4656</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7175</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6744</v>
+        <v>0.1862</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0406</v>
+        <v>1.1784</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0017</v>
+        <v>0.3438</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0423</v>
+        <v>0.8345</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8147</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1909</v>
+        <v>0.9176</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7561</v>
+        <v>0.0507</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5653</v>
+        <v>0.8669</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1082</v>
+        <v>0.6162</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2689</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7246</v>
+        <v>0.7895</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1915</v>
+        <v>1.1888</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4668</v>
+        <v>-0.3994</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7706</v>
+        <v>0.7731</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1703</v>
+        <v>-0.1668</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9409</v>
+        <v>0.9399</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1915</v>
+        <v>1.1888</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1568</v>
+        <v>1.1543</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4209</v>
+        <v>-0.4157</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2859</v>
+        <v>-0.1281</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6924</v>
+        <v>-1.7164</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4065</v>
+        <v>1.5883</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0375</v>
+        <v>-0.0401</v>
       </c>
       <c r="H19" t="n">
-        <v>1.378</v>
+        <v>1.3813</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4154</v>
+        <v>-1.4214</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7367</v>
+        <v>-0.7591</v>
       </c>
       <c r="K19" t="n">
-        <v>0.876</v>
+        <v>0.8651</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.6127</v>
+        <v>-1.6242</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6992</v>
+        <v>0.719</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3145</v>
+        <v>-0.1579</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1785</v>
+        <v>0.1808</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.493</v>
+        <v>-0.3388</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3663</v>
+        <v>-0.258</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2087</v>
+        <v>1.085</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.575</v>
+        <v>-1.343</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4554</v>
+        <v>-0.4466</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0591</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5144</v>
+        <v>-0.5123</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9058</v>
+        <v>0.9018</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3612</v>
+        <v>-1.3485</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3756</v>
+        <v>-0.2742</v>
       </c>
       <c r="T20" t="n">
-        <v>0.369</v>
+        <v>0.253</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7446</v>
+        <v>-0.5272</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2378</v>
+        <v>0.2352</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0771</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8864</v>
+        <v>-0.3382</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5336</v>
+        <v>-1.3347</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6472</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2754</v>
+        <v>-2.2797</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9958</v>
+        <v>-0.983</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2796</v>
+        <v>-1.2967</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3806</v>
+        <v>-2.4107</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7328</v>
+        <v>-1.7589</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1052</v>
+        <v>0.131</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4521</v>
+        <v>0.1008</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1815</v>
+        <v>0.4221</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.3213</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. GOLDEN</t>
+          <t>R. OBASOHAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0923</v>
+        <v>-0.8027</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.905</v>
+        <v>-0.7307</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8127</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4034</v>
+        <v>-0.478</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5927</v>
+        <v>-2.395</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1893</v>
+        <v>1.917</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3799</v>
+        <v>-1.213</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.5291</v>
+        <v>-2.7244</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1493</v>
+        <v>1.5114</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0236</v>
+        <v>0.7351</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0636</v>
+        <v>0.3294</v>
       </c>
       <c r="O22" t="n">
-        <v>0.04</v>
+        <v>0.4057</v>
       </c>
       <c r="P22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>2.5039</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0499</v>
+        <v>0.1729</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4748</v>
+        <v>0.2154</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.0425</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.8634</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.405</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>G. GOLDEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.75</v>
+        <v>-0.9423</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2726</v>
+        <v>-1.9249</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4774</v>
+        <v>0.9826</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4028</v>
+        <v>-2.4159</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5152</v>
+        <v>-2.6098</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8875999999999999</v>
+        <v>0.1939</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1266</v>
+        <v>-2.4031</v>
       </c>
       <c r="K23" t="n">
-        <v>0.052</v>
+        <v>-2.552</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0746</v>
+        <v>0.1489</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5294</v>
+        <v>-0.0129</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5672</v>
+        <v>-0.0578</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9622000000000001</v>
+        <v>0.0449</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7098</v>
+        <v>0.1078</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9618</v>
+        <v>0.4782</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2519</v>
+        <v>-0.3703</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0771</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0771</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. OBASOHAN</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4609</v>
+        <v>-2.0025</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7476</v>
+        <v>-0.6289</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7133</v>
+        <v>-1.3736</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4703</v>
+        <v>-1.3934</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3894</v>
+        <v>-0.5087</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9192</v>
+        <v>-0.8847</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1777</v>
+        <v>0.1262</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.7023</v>
+        <v>0.0517</v>
       </c>
       <c r="L24" t="n">
-        <v>1.5246</v>
+        <v>0.0745</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7074</v>
+        <v>-1.5196</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3129</v>
+        <v>-0.5604</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3946</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4952</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4877</v>
+        <v>0.4517</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8498</v>
+        <v>0.6108</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6379</v>
+        <v>-0.159</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.8639</v>
+        <v>0.0774</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.278</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1781</v>
+        <v>-3.7302</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7804</v>
+        <v>-4.0959</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3976</v>
+        <v>0.3657</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.5526</v>
+        <v>-3.5922</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.8884</v>
+        <v>-3.9133</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3357</v>
+        <v>0.3211</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.7284</v>
+        <v>-2.8035</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.4536</v>
+        <v>-2.5045</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.2747</v>
+        <v>-0.299</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8242</v>
+        <v>-0.7886</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4347</v>
+        <v>-1.4087</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0901</v>
+        <v>0.3992</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2824</v>
+        <v>1.0538</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.3725</v>
+        <v>-0.6546</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3085</v>
+        <v>-0.3096</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.4692</v>
+        <v>-0.4673</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9698999999999995</v>
+        <v>2.2034</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.4252</v>
+        <v>-2.711000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4556</v>
+        <v>4.914400000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.1567</v>
+        <v>-2.1791</v>
       </c>
       <c r="H26" t="n">
-        <v>-9.1266</v>
+        <v>-9.119400000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>6.970200000000001</v>
+        <v>6.9403</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1424999999999996</v>
+        <v>-0.4024000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.7259</v>
+        <v>-5.879200000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>5.583500000000002</v>
+        <v>5.4771</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.0142</v>
+        <v>-1.7767</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.400700000000001</v>
+        <v>-3.2399</v>
       </c>
       <c r="O26" t="n">
-        <v>1.3867</v>
+        <v>1.4632</v>
       </c>
       <c r="P26" t="n">
-        <v>6.805</v>
+        <v>6.829000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-10.2075</v>
+        <v>-10.2434</v>
       </c>
       <c r="R26" t="n">
-        <v>17.0124</v>
+        <v>17.0723</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8618</v>
+        <v>2.2983</v>
       </c>
       <c r="T26" t="n">
-        <v>4.0681</v>
+        <v>4.1066</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.9299</v>
+        <v>-1.8083</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.7563</v>
+        <v>-4.744899999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>3.8566</v>
+        <v>3.8282</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.613000000000001</v>
+        <v>-8.572899999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104535_W9.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104535_W9.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-3.6704</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0121</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.2593</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.4673</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104535_W9.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-8.572899999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
